--- a/human_resources_surveys/008_hr_responsiveness_evaluation_survey--human_resources_surveys.xlsx
+++ b/human_resources_surveys/008_hr_responsiveness_evaluation_survey--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Question2 Comment</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Question3 Comment</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Question4 Comment</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -827,8 +827,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'most_of_the_time'}</t>
+          <t>most_of_the_time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Most of the time'}</t>
+          <t>Most of the time</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
